--- a/nonlinear_gradient_descent_rmse.xlsx
+++ b/nonlinear_gradient_descent_rmse.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{29C82CB0-677B-4B29-8EF9-7E3E407D1043}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E15F0977-CEF7-4CE0-9803-1EAC8E2349EF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="43095" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="9">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="25" uniqueCount="5">
   <si>
     <t>SNR</t>
   </si>
@@ -34,18 +34,6 @@
     <t>rmse</t>
   </si>
   <si>
-    <t>Sum</t>
-  </si>
-  <si>
-    <t>Average</t>
-  </si>
-  <si>
-    <t>Running Total</t>
-  </si>
-  <si>
-    <t>Count</t>
-  </si>
-  <si>
     <t>learning rate</t>
   </si>
 </sst>
@@ -53,12 +41,13 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="3">
+  <numFmts count="4">
     <numFmt numFmtId="164" formatCode="0.00000"/>
     <numFmt numFmtId="165" formatCode="0.0000"/>
     <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.0"/>
   </numFmts>
-  <fonts count="2" x14ac:knownFonts="1">
+  <fonts count="3">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -70,6 +59,11 @@
       <color theme="1"/>
       <name val="Arial"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial Unicode MS"/>
     </font>
   </fonts>
   <fills count="2">
@@ -92,13 +86,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -317,29 +315,32 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
-  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:X31"/>
+  <sheetFormatPr defaultColWidth="12.5703125" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="11.7109375" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="13.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:24" ht="12.75">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="K1" t="s">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="P1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
+        <v>4</v>
+      </c>
+      <c r="U1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" ht="12.75">
       <c r="A2" s="3">
         <v>1.0000000000000001E-5</v>
       </c>
@@ -352,9 +353,12 @@
       <c r="P2" s="2">
         <v>0.01</v>
       </c>
-    </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.2"/>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U2" s="6">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" ht="12.75"/>
+    <row r="4" spans="1:24" ht="12.75">
       <c r="A4" s="1" t="s">
         <v>0</v>
       </c>
@@ -403,8 +407,20 @@
       <c r="S4" s="1" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U4" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="V4" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="W4" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="X4" s="1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" ht="12.75">
       <c r="A5" s="1">
         <v>20</v>
       </c>
@@ -453,8 +469,20 @@
       <c r="S5" s="1">
         <v>2.3784426669888701</v>
       </c>
-    </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U5" s="1">
+        <v>20</v>
+      </c>
+      <c r="V5" s="1">
+        <v>2</v>
+      </c>
+      <c r="W5" s="1">
+        <v>4</v>
+      </c>
+      <c r="X5" s="7">
+        <v>0.86841678903400099</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" ht="12.75">
       <c r="A6" s="1">
         <v>20</v>
       </c>
@@ -503,8 +531,20 @@
       <c r="S6" s="1">
         <v>0.23174969946603199</v>
       </c>
-    </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U6" s="1">
+        <v>20</v>
+      </c>
+      <c r="V6" s="1">
+        <v>2</v>
+      </c>
+      <c r="W6" s="1">
+        <v>5</v>
+      </c>
+      <c r="X6" s="7">
+        <v>0.57135838856508603</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" ht="12.75">
       <c r="A7" s="1">
         <v>20</v>
       </c>
@@ -553,8 +593,20 @@
       <c r="S7" s="1">
         <v>0.80243044012643605</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U7" s="1">
+        <v>20</v>
+      </c>
+      <c r="V7" s="1">
+        <v>2</v>
+      </c>
+      <c r="W7" s="1">
+        <v>6</v>
+      </c>
+      <c r="X7" s="7">
+        <v>0.39889886607554398</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" ht="12.75">
       <c r="A8" s="1">
         <v>20</v>
       </c>
@@ -603,8 +655,20 @@
       <c r="S8" s="1">
         <v>1.0171444242183501</v>
       </c>
-    </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U8" s="1">
+        <v>20</v>
+      </c>
+      <c r="V8" s="1">
+        <v>5</v>
+      </c>
+      <c r="W8" s="1">
+        <v>4</v>
+      </c>
+      <c r="X8" s="7">
+        <v>1.74803506288904</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" ht="12.75">
       <c r="A9" s="1">
         <v>20</v>
       </c>
@@ -653,8 +717,20 @@
       <c r="S9" s="1">
         <v>0.69350117573717496</v>
       </c>
-    </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U9" s="1">
+        <v>20</v>
+      </c>
+      <c r="V9" s="1">
+        <v>5</v>
+      </c>
+      <c r="W9" s="1">
+        <v>5</v>
+      </c>
+      <c r="X9" s="7">
+        <v>3.3980140860538</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" ht="12.75">
       <c r="A10" s="1">
         <v>20</v>
       </c>
@@ -703,8 +779,20 @@
       <c r="S10" s="1">
         <v>0.96923744407458301</v>
       </c>
-    </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U10" s="1">
+        <v>20</v>
+      </c>
+      <c r="V10" s="1">
+        <v>5</v>
+      </c>
+      <c r="W10" s="1">
+        <v>6</v>
+      </c>
+      <c r="X10" s="7">
+        <v>1.9645555462508699</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" ht="12.75">
       <c r="A11" s="1">
         <v>20</v>
       </c>
@@ -753,8 +841,20 @@
       <c r="S11" s="1">
         <v>1.9372808911230901</v>
       </c>
-    </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U11" s="1">
+        <v>20</v>
+      </c>
+      <c r="V11" s="1">
+        <v>10</v>
+      </c>
+      <c r="W11" s="1">
+        <v>4</v>
+      </c>
+      <c r="X11" s="7">
+        <v>3.2460575493046102</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" ht="12.75">
       <c r="A12" s="1">
         <v>20</v>
       </c>
@@ -803,8 +903,20 @@
       <c r="S12" s="1">
         <v>1.27976781180392</v>
       </c>
-    </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U12" s="1">
+        <v>20</v>
+      </c>
+      <c r="V12" s="1">
+        <v>10</v>
+      </c>
+      <c r="W12" s="1">
+        <v>5</v>
+      </c>
+      <c r="X12" s="7">
+        <v>4.1408144711592803</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" ht="12.75">
       <c r="A13" s="1">
         <v>20</v>
       </c>
@@ -853,8 +965,20 @@
       <c r="S13" s="1">
         <v>0.93925950673634495</v>
       </c>
-    </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U13" s="1">
+        <v>20</v>
+      </c>
+      <c r="V13" s="1">
+        <v>10</v>
+      </c>
+      <c r="W13" s="1">
+        <v>6</v>
+      </c>
+      <c r="X13" s="7">
+        <v>7.1119296117742499</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" ht="12.75">
       <c r="A14" s="1">
         <v>40</v>
       </c>
@@ -903,8 +1027,20 @@
       <c r="S14" s="1">
         <v>0.92642491747562705</v>
       </c>
-    </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U14" s="1">
+        <v>40</v>
+      </c>
+      <c r="V14" s="1">
+        <v>2</v>
+      </c>
+      <c r="W14" s="1">
+        <v>4</v>
+      </c>
+      <c r="X14" s="7">
+        <v>0.24678351258117601</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" ht="12.75">
       <c r="A15" s="1">
         <v>40</v>
       </c>
@@ -953,8 +1089,20 @@
       <c r="S15" s="1">
         <v>6.79958728266776E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U15" s="1">
+        <v>40</v>
+      </c>
+      <c r="V15" s="1">
+        <v>2</v>
+      </c>
+      <c r="W15" s="1">
+        <v>5</v>
+      </c>
+      <c r="X15" s="7">
+        <v>2.30987851354796</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" ht="12.75">
       <c r="A16" s="1">
         <v>40</v>
       </c>
@@ -1003,8 +1151,20 @@
       <c r="S16" s="1">
         <v>2.5178384208198502E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U16" s="1">
+        <v>40</v>
+      </c>
+      <c r="V16" s="1">
+        <v>2</v>
+      </c>
+      <c r="W16" s="1">
+        <v>6</v>
+      </c>
+      <c r="X16" s="7">
+        <v>0.46108321620710702</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" ht="12.75">
       <c r="A17" s="1">
         <v>40</v>
       </c>
@@ -1053,8 +1213,20 @@
       <c r="S17" s="1">
         <v>0.62460503747552998</v>
       </c>
-    </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U17" s="1">
+        <v>40</v>
+      </c>
+      <c r="V17" s="1">
+        <v>5</v>
+      </c>
+      <c r="W17" s="1">
+        <v>4</v>
+      </c>
+      <c r="X17" s="7">
+        <v>10.896079197328101</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" ht="12.75">
       <c r="A18" s="1">
         <v>40</v>
       </c>
@@ -1103,8 +1275,20 @@
       <c r="S18" s="1">
         <v>0.94551502602405801</v>
       </c>
-    </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U18" s="1">
+        <v>40</v>
+      </c>
+      <c r="V18" s="1">
+        <v>5</v>
+      </c>
+      <c r="W18" s="1">
+        <v>5</v>
+      </c>
+      <c r="X18" s="7">
+        <v>1.54633474086762</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" ht="12.75">
       <c r="A19" s="1">
         <v>40</v>
       </c>
@@ -1153,8 +1337,20 @@
       <c r="S19" s="1">
         <v>1.13744359665484</v>
       </c>
-    </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U19" s="1">
+        <v>40</v>
+      </c>
+      <c r="V19" s="1">
+        <v>5</v>
+      </c>
+      <c r="W19" s="1">
+        <v>6</v>
+      </c>
+      <c r="X19" s="7">
+        <v>1.7868515803932801</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" ht="12.75">
       <c r="A20" s="1">
         <v>40</v>
       </c>
@@ -1203,8 +1399,20 @@
       <c r="S20" s="1">
         <v>0.87160926745406198</v>
       </c>
-    </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U20" s="1">
+        <v>40</v>
+      </c>
+      <c r="V20" s="1">
+        <v>10</v>
+      </c>
+      <c r="W20" s="1">
+        <v>4</v>
+      </c>
+      <c r="X20" s="7">
+        <v>1.2707713769448299</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" ht="12.75">
       <c r="A21" s="1">
         <v>40</v>
       </c>
@@ -1253,8 +1461,20 @@
       <c r="S21" s="1">
         <v>1.0098738588526499</v>
       </c>
-    </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U21" s="1">
+        <v>40</v>
+      </c>
+      <c r="V21" s="1">
+        <v>10</v>
+      </c>
+      <c r="W21" s="1">
+        <v>5</v>
+      </c>
+      <c r="X21" s="7">
+        <v>9.2865233348616893</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" ht="12.75">
       <c r="A22" s="1">
         <v>40</v>
       </c>
@@ -1303,8 +1523,20 @@
       <c r="S22" s="1">
         <v>0.71187654079436302</v>
       </c>
-    </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U22" s="1">
+        <v>40</v>
+      </c>
+      <c r="V22" s="1">
+        <v>10</v>
+      </c>
+      <c r="W22" s="1">
+        <v>6</v>
+      </c>
+      <c r="X22" s="7">
+        <v>11.227955317233199</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" ht="12.75">
       <c r="A23" s="1">
         <v>80</v>
       </c>
@@ -1353,8 +1585,20 @@
       <c r="S23" s="1">
         <v>8.1262314085045698E-3</v>
       </c>
-    </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U23" s="1">
+        <v>80</v>
+      </c>
+      <c r="V23" s="1">
+        <v>2</v>
+      </c>
+      <c r="W23" s="1">
+        <v>4</v>
+      </c>
+      <c r="X23" s="7">
+        <v>5.01850284709609</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" ht="12.75">
       <c r="A24" s="1">
         <v>80</v>
       </c>
@@ -1403,8 +1647,20 @@
       <c r="S24" s="1">
         <v>0.77904153136208898</v>
       </c>
-    </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U24" s="1">
+        <v>80</v>
+      </c>
+      <c r="V24" s="1">
+        <v>2</v>
+      </c>
+      <c r="W24" s="1">
+        <v>5</v>
+      </c>
+      <c r="X24" s="7">
+        <v>0.48261287006989101</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" ht="12.75">
       <c r="A25" s="1">
         <v>80</v>
       </c>
@@ -1453,8 +1709,20 @@
       <c r="S25" s="1">
         <v>1.22530783304258</v>
       </c>
-    </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U25" s="1">
+        <v>80</v>
+      </c>
+      <c r="V25" s="1">
+        <v>2</v>
+      </c>
+      <c r="W25" s="1">
+        <v>6</v>
+      </c>
+      <c r="X25" s="7">
+        <v>0.185784770912685</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" ht="12.75">
       <c r="A26" s="1">
         <v>80</v>
       </c>
@@ -1503,8 +1771,20 @@
       <c r="S26" s="1">
         <v>0.60593554447424602</v>
       </c>
-    </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U26" s="1">
+        <v>80</v>
+      </c>
+      <c r="V26" s="1">
+        <v>5</v>
+      </c>
+      <c r="W26" s="1">
+        <v>4</v>
+      </c>
+      <c r="X26" s="7">
+        <v>1.2825867076408199</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" ht="12.75">
       <c r="A27" s="1">
         <v>80</v>
       </c>
@@ -1553,8 +1833,20 @@
       <c r="S27" s="1">
         <v>0.879850467827755</v>
       </c>
-    </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="U27" s="1">
+        <v>80</v>
+      </c>
+      <c r="V27" s="1">
+        <v>5</v>
+      </c>
+      <c r="W27" s="1">
+        <v>5</v>
+      </c>
+      <c r="X27" s="7">
+        <v>8.7999056179061803</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" ht="12.75">
       <c r="A28" s="1">
         <v>80</v>
       </c>
@@ -1603,8 +1895,20 @@
       <c r="S28" s="1">
         <v>0.73535795159633</v>
       </c>
-    </row>
-    <row r="29" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U28" s="1">
+        <v>80</v>
+      </c>
+      <c r="V28" s="1">
+        <v>5</v>
+      </c>
+      <c r="W28" s="1">
+        <v>6</v>
+      </c>
+      <c r="X28" s="7">
+        <v>2.80539300460241</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" ht="15.75" customHeight="1">
       <c r="A29" s="1">
         <v>80</v>
       </c>
@@ -1653,8 +1957,20 @@
       <c r="S29" s="1">
         <v>0.69761966604455405</v>
       </c>
-    </row>
-    <row r="30" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U29" s="1">
+        <v>80</v>
+      </c>
+      <c r="V29" s="1">
+        <v>10</v>
+      </c>
+      <c r="W29" s="1">
+        <v>4</v>
+      </c>
+      <c r="X29" s="7">
+        <v>4.5634646746730896</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" ht="15.75" customHeight="1">
       <c r="A30" s="1">
         <v>80</v>
       </c>
@@ -1703,8 +2019,20 @@
       <c r="S30" s="1">
         <v>1.0350329247389101</v>
       </c>
-    </row>
-    <row r="31" spans="1:19" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="U30" s="1">
+        <v>80</v>
+      </c>
+      <c r="V30" s="1">
+        <v>10</v>
+      </c>
+      <c r="W30" s="1">
+        <v>5</v>
+      </c>
+      <c r="X30" s="7">
+        <v>1.53119553654098</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" ht="15.75" customHeight="1">
       <c r="A31" s="1">
         <v>80</v>
       </c>
@@ -1752,6 +2080,18 @@
       </c>
       <c r="S31" s="1">
         <v>1.0350329247389101</v>
+      </c>
+      <c r="U31" s="1">
+        <v>80</v>
+      </c>
+      <c r="V31" s="1">
+        <v>10</v>
+      </c>
+      <c r="W31" s="1">
+        <v>6</v>
+      </c>
+      <c r="X31" s="7">
+        <v>2.0740927853890998</v>
       </c>
     </row>
   </sheetData>
